--- a/outputs/cumulative_motion_statistics.xlsx
+++ b/outputs/cumulative_motion_statistics.xlsx
@@ -441,10 +441,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15149.60308937927</v>
+        <v>868008.3183197853</v>
       </c>
       <c r="C2" t="n">
-        <v>17467.51276177058</v>
+        <v>1000814.759840359</v>
       </c>
     </row>
     <row r="3">
@@ -454,10 +454,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19398.08254855897</v>
+        <v>1111428.260678805</v>
       </c>
       <c r="C3" t="n">
-        <v>19499.19261239494</v>
+        <v>1117221.440602904</v>
       </c>
     </row>
     <row r="4">
@@ -467,10 +467,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7370.600732218009</v>
+        <v>422304.3144321262</v>
       </c>
       <c r="C4" t="n">
-        <v>9154.809543875175</v>
+        <v>524531.9491101338</v>
       </c>
     </row>
     <row r="5">
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7755.942344220794</v>
+        <v>444382.7624706535</v>
       </c>
       <c r="C5" t="n">
-        <v>6007.159162004034</v>
+        <v>344184.8668461755</v>
       </c>
     </row>
     <row r="6">
@@ -493,10 +493,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26538.1568968298</v>
+        <v>1520524.386244345</v>
       </c>
       <c r="C6" t="n">
-        <v>27373.58243922011</v>
+        <v>1568390.743920737</v>
       </c>
     </row>
     <row r="7">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9309.827607109573</v>
+        <v>533413.8298817569</v>
       </c>
       <c r="C7" t="n">
-        <v>7812.593924292049</v>
+        <v>447628.6589114838</v>
       </c>
     </row>
     <row r="8">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10169.4119258939</v>
+        <v>582664.3834837268</v>
       </c>
       <c r="C8" t="n">
-        <v>16296.66339063943</v>
+        <v>933730.0324289976</v>
       </c>
     </row>
     <row r="9">
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13911.20193557838</v>
+        <v>797053.1588628626</v>
       </c>
       <c r="C9" t="n">
-        <v>13072.54596751061</v>
+        <v>749001.7114291216</v>
       </c>
     </row>
     <row r="10">
@@ -545,10 +545,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10518.75454174541</v>
+        <v>602680.2409760782</v>
       </c>
       <c r="C10" t="n">
-        <v>9881.914219836446</v>
+        <v>566191.978306942</v>
       </c>
     </row>
     <row r="11">
@@ -558,10 +558,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20046.33529756153</v>
+        <v>1148570.407254405</v>
       </c>
       <c r="C11" t="n">
-        <v>19394.28672124085</v>
+        <v>1111210.775793716</v>
       </c>
     </row>
     <row r="12">
@@ -571,10 +571,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12041.60781965383</v>
+        <v>689933.3066178939</v>
       </c>
       <c r="C12" t="n">
-        <v>12757.86818740577</v>
+        <v>730972.0027225683</v>
       </c>
     </row>
     <row r="13">
@@ -584,10 +584,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7219.582203575893</v>
+        <v>413651.5901126574</v>
       </c>
       <c r="C13" t="n">
-        <v>10690.12483508874</v>
+        <v>612499.0355185702</v>
       </c>
     </row>
     <row r="14">
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11332.17206140879</v>
+        <v>649285.6318347899</v>
       </c>
       <c r="C14" t="n">
-        <v>13051.5990658227</v>
+        <v>747801.5423685283</v>
       </c>
     </row>
     <row r="15">
@@ -610,10 +610,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10478.8117376896</v>
+        <v>600391.6868817623</v>
       </c>
       <c r="C15" t="n">
-        <v>9251.11781183958</v>
+        <v>530050.0063967092</v>
       </c>
     </row>
     <row r="16">
@@ -623,10 +623,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8365.161836602245</v>
+        <v>479288.468181213</v>
       </c>
       <c r="C16" t="n">
-        <v>6956.647770168286</v>
+        <v>398586.5567897379</v>
       </c>
     </row>
     <row r="17">
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11582.95142675432</v>
+        <v>663654.2310580576</v>
       </c>
       <c r="C17" t="n">
-        <v>11960.42411651058</v>
+        <v>685281.8230625424</v>
       </c>
     </row>
     <row r="18">
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13019.92156370073</v>
+        <v>745986.5551914234</v>
       </c>
       <c r="C18" t="n">
-        <v>13125.08729456734</v>
+        <v>752012.1077194887</v>
       </c>
     </row>
     <row r="19">
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5284.944803284069</v>
+        <v>302805.0321877743</v>
       </c>
       <c r="C19" t="n">
-        <v>5327.477792808078</v>
+        <v>305241.9929775741</v>
       </c>
     </row>
     <row r="20">
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7353.771188689632</v>
+        <v>421340.0526168185</v>
       </c>
       <c r="C20" t="n">
-        <v>6838.198884789373</v>
+        <v>391799.9355694973</v>
       </c>
     </row>
   </sheetData>
@@ -737,16 +737,16 @@
         <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>11939.30745055025</v>
+        <v>684071.9272256281</v>
       </c>
       <c r="D2" t="n">
-        <v>5287.727607548481</v>
+        <v>302964.475127336</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.065044201242645</v>
+        <v>-1.065044201242643</v>
       </c>
       <c r="F2" t="n">
-        <v>0.300934784170967</v>
+        <v>0.3009347841709681</v>
       </c>
     </row>
     <row r="3">
@@ -759,16 +759,16 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>12416.77928956762</v>
+        <v>711429.048437673</v>
       </c>
       <c r="D3" t="n">
-        <v>5619.00132577294</v>
+        <v>321945.0610452036</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.065044201242645</v>
+        <v>-1.065044201242643</v>
       </c>
       <c r="F3" t="n">
-        <v>0.300934784170967</v>
+        <v>0.3009347841709681</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cumulative_motion_statistics.xlsx
+++ b/outputs/cumulative_motion_statistics.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="cumulative_rotation_by_arm" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="rotation_data_by_arm" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="cumulative_rotation_summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="rotation_rate_summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -425,12 +426,27 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Operated</t>
+          <t>Operated cumulative rotation</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Non-operated</t>
+          <t>Non-operated cumulative rotation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Operated rotation rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Non-operated rotation rate</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Mocap duration (hours)</t>
         </is>
       </c>
     </row>
@@ -446,6 +462,15 @@
       <c r="C2" t="n">
         <v>1000814.759840359</v>
       </c>
+      <c r="D2" t="n">
+        <v>77172.87283814614</v>
+      </c>
+      <c r="E2" t="n">
+        <v>88980.42629960732</v>
+      </c>
+      <c r="F2" t="n">
+        <v>11.24758333333333</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -459,6 +484,15 @@
       <c r="C3" t="n">
         <v>1117221.440602904</v>
       </c>
+      <c r="D3" t="n">
+        <v>87183.19017821037</v>
+      </c>
+      <c r="E3" t="n">
+        <v>87637.62158411226</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12.74819444444444</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -472,6 +506,15 @@
       <c r="C4" t="n">
         <v>524531.9491101338</v>
       </c>
+      <c r="D4" t="n">
+        <v>65044.38981207769</v>
+      </c>
+      <c r="E4" t="n">
+        <v>80789.75137321727</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6.492555555555556</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -485,6 +528,15 @@
       <c r="C5" t="n">
         <v>344184.8668461755</v>
       </c>
+      <c r="D5" t="n">
+        <v>54346.00602965504</v>
+      </c>
+      <c r="E5" t="n">
+        <v>42092.2556602846</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8.176916666666667</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -498,6 +550,15 @@
       <c r="C6" t="n">
         <v>1568390.743920737</v>
       </c>
+      <c r="D6" t="n">
+        <v>108652.6476036904</v>
+      </c>
+      <c r="E6" t="n">
+        <v>112073.0508144085</v>
+      </c>
+      <c r="F6" t="n">
+        <v>13.99436111111111</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -511,6 +572,15 @@
       <c r="C7" t="n">
         <v>447628.6589114838</v>
       </c>
+      <c r="D7" t="n">
+        <v>43545.76349089816</v>
+      </c>
+      <c r="E7" t="n">
+        <v>36542.6065481435</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12.2495</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -524,6 +594,15 @@
       <c r="C8" t="n">
         <v>933730.0324289976</v>
       </c>
+      <c r="D8" t="n">
+        <v>48577.06754502397</v>
+      </c>
+      <c r="E8" t="n">
+        <v>77845.61428472423</v>
+      </c>
+      <c r="F8" t="n">
+        <v>11.99463888888889</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -537,6 +616,15 @@
       <c r="C9" t="n">
         <v>749001.7114291216</v>
       </c>
+      <c r="D9" t="n">
+        <v>56938.13008670133</v>
+      </c>
+      <c r="E9" t="n">
+        <v>53505.53649565407</v>
+      </c>
+      <c r="F9" t="n">
+        <v>13.99858333333333</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -550,6 +638,15 @@
       <c r="C10" t="n">
         <v>566191.978306942</v>
       </c>
+      <c r="D10" t="n">
+        <v>135224.4258273012</v>
+      </c>
+      <c r="E10" t="n">
+        <v>127037.4901466513</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.456888888888889</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -563,6 +660,15 @@
       <c r="C11" t="n">
         <v>1111210.775793716</v>
       </c>
+      <c r="D11" t="n">
+        <v>89426.4064042359</v>
+      </c>
+      <c r="E11" t="n">
+        <v>86517.6273124061</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12.84375</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -576,6 +682,15 @@
       <c r="C12" t="n">
         <v>730972.0027225683</v>
       </c>
+      <c r="D12" t="n">
+        <v>53214.95012918123</v>
+      </c>
+      <c r="E12" t="n">
+        <v>56380.28820697659</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12.96502777777778</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -589,6 +704,15 @@
       <c r="C13" t="n">
         <v>612499.0355185702</v>
       </c>
+      <c r="D13" t="n">
+        <v>51170.40325498396</v>
+      </c>
+      <c r="E13" t="n">
+        <v>75768.65021173515</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8.083805555555555</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -602,6 +726,15 @@
       <c r="C14" t="n">
         <v>747801.5423685283</v>
       </c>
+      <c r="D14" t="n">
+        <v>42695.40527823177</v>
+      </c>
+      <c r="E14" t="n">
+        <v>49173.56607582392</v>
+      </c>
+      <c r="F14" t="n">
+        <v>15.20738888888889</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -615,6 +748,15 @@
       <c r="C15" t="n">
         <v>530050.0063967092</v>
       </c>
+      <c r="D15" t="n">
+        <v>55844.61742389273</v>
+      </c>
+      <c r="E15" t="n">
+        <v>49301.88153751946</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10.75111111111111</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -628,6 +770,15 @@
       <c r="C16" t="n">
         <v>398586.5567897379</v>
       </c>
+      <c r="D16" t="n">
+        <v>39937.74733011367</v>
+      </c>
+      <c r="E16" t="n">
+        <v>33213.0861705396</v>
+      </c>
+      <c r="F16" t="n">
+        <v>12.00088888888889</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -641,6 +792,15 @@
       <c r="C17" t="n">
         <v>685281.8230625424</v>
       </c>
+      <c r="D17" t="n">
+        <v>75326.08912458445</v>
+      </c>
+      <c r="E17" t="n">
+        <v>77780.8642870703</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8.810416666666667</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -654,6 +814,15 @@
       <c r="C18" t="n">
         <v>752012.1077194887</v>
       </c>
+      <c r="D18" t="n">
+        <v>77690.29775711001</v>
+      </c>
+      <c r="E18" t="n">
+        <v>78317.82511239374</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9.602055555555555</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -667,6 +836,15 @@
       <c r="C19" t="n">
         <v>305241.9929775741</v>
       </c>
+      <c r="D19" t="n">
+        <v>44675.41990606659</v>
+      </c>
+      <c r="E19" t="n">
+        <v>45034.96560381251</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.77788888888889</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -679,6 +857,15 @@
       </c>
       <c r="C20" t="n">
         <v>391799.9355694973</v>
+      </c>
+      <c r="D20" t="n">
+        <v>59907.11501842631</v>
+      </c>
+      <c r="E20" t="n">
+        <v>55707.03202460507</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7.033222222222221</v>
       </c>
     </row>
   </sheetData>
@@ -692,7 +879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -718,10 +905,15 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>CofV</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>t-statistic</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>p-value</t>
         </is>
@@ -743,9 +935,12 @@
         <v>302964.475127336</v>
       </c>
       <c r="E2" t="n">
+        <v>0.4428839469499368</v>
+      </c>
+      <c r="F2" t="n">
         <v>-1.065044201242643</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.3009347841709681</v>
       </c>
     </row>
@@ -765,10 +960,114 @@
         <v>321945.0610452036</v>
       </c>
       <c r="E3" t="n">
+        <v>0.452532914915701</v>
+      </c>
+      <c r="F3" t="n">
         <v>-1.065044201242643</v>
       </c>
+      <c r="G3" t="n">
+        <v>0.3009347841709681</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Arm</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>CofV</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>t-statistic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>p-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Operated</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C2" t="n">
+        <v>66661.73394939637</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24917.92705614349</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3737965633336054</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.9791278518405865</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3404942585916549</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Non-operated</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3" t="n">
+        <v>69142.11261840451</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25487.86217519956</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3686300752172143</v>
+      </c>
       <c r="F3" t="n">
-        <v>0.3009347841709681</v>
+        <v>-0.9791278518405865</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3404942585916549</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cumulative_motion_statistics.xlsx
+++ b/outputs/cumulative_motion_statistics.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="rotation_data_by_arm" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="cumulative_rotation_summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="rotation_rate_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="demographics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="rotation_data_by_arm" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cumulative_rotation_stats" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="rotation_rate_stats" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,445 +427,783 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Operated cumulative rotation</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Non-operated cumulative rotation</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Operated rotation rate</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Non-operated rotation rate</t>
+          <t>Handedness</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>RTSA side</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>RTSA On Dominant Arm</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Start Time</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Mocap duration (hours)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 2016-5-5</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>868008.3183197853</v>
-      </c>
       <c r="C2" t="n">
-        <v>1000814.759840359</v>
-      </c>
-      <c r="D2" t="n">
-        <v>77172.87283814614</v>
-      </c>
-      <c r="E2" t="n">
-        <v>88980.42629960732</v>
-      </c>
-      <c r="F2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>10:50:50</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>11.24758333333333</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 2016-5-6</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>1111428.260678805</v>
-      </c>
       <c r="C3" t="n">
-        <v>1117221.440602904</v>
-      </c>
-      <c r="D3" t="n">
-        <v>87183.19017821037</v>
-      </c>
-      <c r="E3" t="n">
-        <v>87637.62158411226</v>
-      </c>
-      <c r="F3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>12:16:17</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>12.74819444444444</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 2016-6-22</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>422304.3144321262</v>
-      </c>
       <c r="C4" t="n">
-        <v>524531.9491101338</v>
-      </c>
-      <c r="D4" t="n">
-        <v>65044.38981207769</v>
-      </c>
-      <c r="E4" t="n">
-        <v>80789.75137321727</v>
-      </c>
-      <c r="F4" t="n">
+        <v>78</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>11:33:25</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>6.492555555555556</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 2016-6-23</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>444382.7624706535</v>
-      </c>
       <c r="C5" t="n">
-        <v>344184.8668461755</v>
-      </c>
-      <c r="D5" t="n">
-        <v>54346.00602965504</v>
-      </c>
-      <c r="E5" t="n">
-        <v>42092.2556602846</v>
-      </c>
-      <c r="F5" t="n">
+        <v>84</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>09:38:08</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>8.176916666666667</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 2016-6-30</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>1520524.386244345</v>
-      </c>
       <c r="C6" t="n">
-        <v>1568390.743920737</v>
-      </c>
-      <c r="D6" t="n">
-        <v>108652.6476036904</v>
-      </c>
-      <c r="E6" t="n">
-        <v>112073.0508144085</v>
-      </c>
-      <c r="F6" t="n">
+        <v>63</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>08:33:25</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>13.99436111111111</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 4-20-2015</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>533413.8298817569</v>
-      </c>
       <c r="C7" t="n">
-        <v>447628.6589114838</v>
-      </c>
-      <c r="D7" t="n">
-        <v>43545.76349089816</v>
-      </c>
-      <c r="E7" t="n">
-        <v>36542.6065481435</v>
-      </c>
-      <c r="F7" t="n">
+        <v>72</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>08:47:13</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>12.2495</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 4-29-2015</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>582664.3834837268</v>
-      </c>
       <c r="C8" t="n">
-        <v>933730.0324289976</v>
-      </c>
-      <c r="D8" t="n">
-        <v>48577.06754502397</v>
-      </c>
-      <c r="E8" t="n">
-        <v>77845.61428472423</v>
-      </c>
-      <c r="F8" t="n">
+        <v>56</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>10:08:35</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>11.99463888888889</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 5-06-2015</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>797053.1588628626</v>
-      </c>
       <c r="C9" t="n">
-        <v>749001.7114291216</v>
-      </c>
-      <c r="D9" t="n">
-        <v>56938.13008670133</v>
-      </c>
-      <c r="E9" t="n">
-        <v>53505.53649565407</v>
-      </c>
-      <c r="F9" t="n">
+        <v>71</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>09:08:56</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>13.99858333333333</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 5-11-2015</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>602680.2409760782</v>
-      </c>
       <c r="C10" t="n">
-        <v>566191.978306942</v>
-      </c>
-      <c r="D10" t="n">
-        <v>135224.4258273012</v>
-      </c>
-      <c r="E10" t="n">
-        <v>127037.4901466513</v>
-      </c>
-      <c r="F10" t="n">
+        <v>67</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>08:33:03</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>4.456888888888889</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 5-13-2015</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>1148570.407254405</v>
-      </c>
       <c r="C11" t="n">
-        <v>1111210.775793716</v>
-      </c>
-      <c r="D11" t="n">
-        <v>89426.4064042359</v>
-      </c>
-      <c r="E11" t="n">
-        <v>86517.6273124061</v>
-      </c>
-      <c r="F11" t="n">
+        <v>81</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>09:21:55</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>12.84375</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 5-22-2015</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>689933.3066178939</v>
-      </c>
       <c r="C12" t="n">
-        <v>730972.0027225683</v>
-      </c>
-      <c r="D12" t="n">
-        <v>53214.95012918123</v>
-      </c>
-      <c r="E12" t="n">
-        <v>56380.28820697659</v>
-      </c>
-      <c r="F12" t="n">
+        <v>69</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>08:39:40</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>12.96502777777778</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 5-25-2015</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>413651.5901126574</v>
-      </c>
       <c r="C13" t="n">
-        <v>612499.0355185702</v>
-      </c>
-      <c r="D13" t="n">
-        <v>51170.40325498396</v>
-      </c>
-      <c r="E13" t="n">
-        <v>75768.65021173515</v>
-      </c>
-      <c r="F13" t="n">
+        <v>76</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>10:37:24</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>8.083805555555555</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 5-29-2015</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>649285.6318347899</v>
-      </c>
       <c r="C14" t="n">
-        <v>747801.5423685283</v>
-      </c>
-      <c r="D14" t="n">
-        <v>42695.40527823177</v>
-      </c>
-      <c r="E14" t="n">
-        <v>49173.56607582392</v>
-      </c>
-      <c r="F14" t="n">
+        <v>75</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>08:47:21</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>15.20738888888889</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 6-15-2015</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>600391.6868817623</v>
-      </c>
       <c r="C15" t="n">
-        <v>530050.0063967092</v>
-      </c>
-      <c r="D15" t="n">
-        <v>55844.61742389273</v>
-      </c>
-      <c r="E15" t="n">
-        <v>49301.88153751946</v>
-      </c>
-      <c r="F15" t="n">
+        <v>80</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>10:04:35</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>10.75111111111111</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 6-18-2015</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>479288.468181213</v>
-      </c>
       <c r="C16" t="n">
-        <v>398586.5567897379</v>
-      </c>
-      <c r="D16" t="n">
-        <v>39937.74733011367</v>
-      </c>
-      <c r="E16" t="n">
-        <v>33213.0861705396</v>
-      </c>
-      <c r="F16" t="n">
+        <v>77</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>09:03:43</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>12.00088888888889</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 6-24-2015</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>663654.2310580576</v>
-      </c>
       <c r="C17" t="n">
-        <v>685281.8230625424</v>
-      </c>
-      <c r="D17" t="n">
-        <v>75326.08912458445</v>
-      </c>
-      <c r="E17" t="n">
-        <v>77780.8642870703</v>
-      </c>
-      <c r="F17" t="n">
+        <v>78</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>09:15:16</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>8.810416666666667</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 7-28-2015</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>745986.5551914234</v>
-      </c>
       <c r="C18" t="n">
-        <v>752012.1077194887</v>
-      </c>
-      <c r="D18" t="n">
-        <v>77690.29775711001</v>
-      </c>
-      <c r="E18" t="n">
-        <v>78317.82511239374</v>
-      </c>
-      <c r="F18" t="n">
+        <v>78</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>08:18:41</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>9.602055555555555</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 8-10-2015b (IW) (HUM REVERSED)</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>302805.0321877743</v>
-      </c>
       <c r="C19" t="n">
-        <v>305241.9929775741</v>
-      </c>
-      <c r="D19" t="n">
-        <v>44675.41990606659</v>
-      </c>
-      <c r="E19" t="n">
-        <v>45034.96560381251</v>
-      </c>
-      <c r="F19" t="n">
+        <v>81</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>09:44:47</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>6.77788888888889</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>1_R_MATRICES_NORM 8-13-2015</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>421340.0526168185</v>
-      </c>
       <c r="C20" t="n">
-        <v>391799.9355694973</v>
-      </c>
-      <c r="D20" t="n">
-        <v>59907.11501842631</v>
-      </c>
-      <c r="E20" t="n">
-        <v>55707.03202460507</v>
-      </c>
-      <c r="F20" t="n">
+        <v>79</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>10:17:32</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>7.033222222222221</v>
       </c>
     </row>
@@ -879,94 +1218,519 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Arm</t>
+          <t>participant</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Mean</t>
+          <t>Operated cumulative rotation</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Std</t>
+          <t>Non-operated cumulative rotation</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>CofV</t>
+          <t>Operated rotation rate</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>t-statistic</t>
+          <t>Non-operated rotation rate</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>p-value</t>
+          <t>Mocap duration (hours)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Operated</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>19</v>
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 2016-5-5</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>684071.9272256281</v>
+        <v>868008.3183197853</v>
       </c>
       <c r="D2" t="n">
-        <v>302964.475127336</v>
+        <v>1000814.759840359</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4428839469499368</v>
+        <v>77172.87283814614</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.065044201242643</v>
+        <v>88980.42629960732</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3009347841709681</v>
+        <v>11.24758333333333</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Non-operated</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>19</v>
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 2016-5-6</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>711429.048437673</v>
+        <v>1111428.260678805</v>
       </c>
       <c r="D3" t="n">
-        <v>321945.0610452036</v>
+        <v>1117221.440602904</v>
       </c>
       <c r="E3" t="n">
-        <v>0.452532914915701</v>
+        <v>87183.19017821037</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.065044201242643</v>
+        <v>87637.62158411226</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3009347841709681</v>
+        <v>12.74819444444444</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 2016-6-22</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>422304.3144321262</v>
+      </c>
+      <c r="D4" t="n">
+        <v>524531.9491101338</v>
+      </c>
+      <c r="E4" t="n">
+        <v>65044.38981207769</v>
+      </c>
+      <c r="F4" t="n">
+        <v>80789.75137321727</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.492555555555556</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 2016-6-23</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>444382.7624706535</v>
+      </c>
+      <c r="D5" t="n">
+        <v>344184.8668461755</v>
+      </c>
+      <c r="E5" t="n">
+        <v>54346.00602965504</v>
+      </c>
+      <c r="F5" t="n">
+        <v>42092.2556602846</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8.176916666666667</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 2016-6-30</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1520524.386244345</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1568390.743920737</v>
+      </c>
+      <c r="E6" t="n">
+        <v>108652.6476036904</v>
+      </c>
+      <c r="F6" t="n">
+        <v>112073.0508144085</v>
+      </c>
+      <c r="G6" t="n">
+        <v>13.99436111111111</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 4-20-2015</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>533413.8298817569</v>
+      </c>
+      <c r="D7" t="n">
+        <v>447628.6589114838</v>
+      </c>
+      <c r="E7" t="n">
+        <v>43545.76349089816</v>
+      </c>
+      <c r="F7" t="n">
+        <v>36542.6065481435</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12.2495</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 4-29-2015</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>582664.3834837268</v>
+      </c>
+      <c r="D8" t="n">
+        <v>933730.0324289976</v>
+      </c>
+      <c r="E8" t="n">
+        <v>48577.06754502397</v>
+      </c>
+      <c r="F8" t="n">
+        <v>77845.61428472423</v>
+      </c>
+      <c r="G8" t="n">
+        <v>11.99463888888889</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 5-06-2015</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>797053.1588628626</v>
+      </c>
+      <c r="D9" t="n">
+        <v>749001.7114291216</v>
+      </c>
+      <c r="E9" t="n">
+        <v>56938.13008670133</v>
+      </c>
+      <c r="F9" t="n">
+        <v>53505.53649565407</v>
+      </c>
+      <c r="G9" t="n">
+        <v>13.99858333333333</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 5-11-2015</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>602680.2409760782</v>
+      </c>
+      <c r="D10" t="n">
+        <v>566191.978306942</v>
+      </c>
+      <c r="E10" t="n">
+        <v>135224.4258273012</v>
+      </c>
+      <c r="F10" t="n">
+        <v>127037.4901466513</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.456888888888889</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 5-13-2015</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1148570.407254405</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1111210.775793716</v>
+      </c>
+      <c r="E11" t="n">
+        <v>89426.4064042359</v>
+      </c>
+      <c r="F11" t="n">
+        <v>86517.6273124061</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12.84375</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 5-22-2015</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>689933.3066178939</v>
+      </c>
+      <c r="D12" t="n">
+        <v>730972.0027225683</v>
+      </c>
+      <c r="E12" t="n">
+        <v>53214.95012918123</v>
+      </c>
+      <c r="F12" t="n">
+        <v>56380.28820697659</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12.96502777777778</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 5-25-2015</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>413651.5901126574</v>
+      </c>
+      <c r="D13" t="n">
+        <v>612499.0355185702</v>
+      </c>
+      <c r="E13" t="n">
+        <v>51170.40325498396</v>
+      </c>
+      <c r="F13" t="n">
+        <v>75768.65021173515</v>
+      </c>
+      <c r="G13" t="n">
+        <v>8.083805555555555</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 5-29-2015</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>649285.6318347899</v>
+      </c>
+      <c r="D14" t="n">
+        <v>747801.5423685283</v>
+      </c>
+      <c r="E14" t="n">
+        <v>42695.40527823177</v>
+      </c>
+      <c r="F14" t="n">
+        <v>49173.56607582392</v>
+      </c>
+      <c r="G14" t="n">
+        <v>15.20738888888889</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 6-15-2015</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>600391.6868817623</v>
+      </c>
+      <c r="D15" t="n">
+        <v>530050.0063967092</v>
+      </c>
+      <c r="E15" t="n">
+        <v>55844.61742389273</v>
+      </c>
+      <c r="F15" t="n">
+        <v>49301.88153751946</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10.75111111111111</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 6-18-2015</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>479288.468181213</v>
+      </c>
+      <c r="D16" t="n">
+        <v>398586.5567897379</v>
+      </c>
+      <c r="E16" t="n">
+        <v>39937.74733011367</v>
+      </c>
+      <c r="F16" t="n">
+        <v>33213.0861705396</v>
+      </c>
+      <c r="G16" t="n">
+        <v>12.00088888888889</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 6-24-2015</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>663654.2310580576</v>
+      </c>
+      <c r="D17" t="n">
+        <v>685281.8230625424</v>
+      </c>
+      <c r="E17" t="n">
+        <v>75326.08912458445</v>
+      </c>
+      <c r="F17" t="n">
+        <v>77780.8642870703</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8.810416666666667</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 7-28-2015</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>745986.5551914234</v>
+      </c>
+      <c r="D18" t="n">
+        <v>752012.1077194887</v>
+      </c>
+      <c r="E18" t="n">
+        <v>77690.29775711001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>78317.82511239374</v>
+      </c>
+      <c r="G18" t="n">
+        <v>9.602055555555555</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 8-10-2015b (IW) (HUM REVERSED)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>302805.0321877743</v>
+      </c>
+      <c r="D19" t="n">
+        <v>305241.9929775741</v>
+      </c>
+      <c r="E19" t="n">
+        <v>44675.41990606659</v>
+      </c>
+      <c r="F19" t="n">
+        <v>45034.96560381251</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6.77788888888889</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1_R_MATRICES_NORM 8-13-2015</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>421340.0526168185</v>
+      </c>
+      <c r="D20" t="n">
+        <v>391799.9355694973</v>
+      </c>
+      <c r="E20" t="n">
+        <v>59907.11501842631</v>
+      </c>
+      <c r="F20" t="n">
+        <v>55707.03202460507</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7.033222222222221</v>
       </c>
     </row>
   </sheetData>
@@ -1030,6 +1794,107 @@
         <v>19</v>
       </c>
       <c r="C2" t="n">
+        <v>684071.9272256281</v>
+      </c>
+      <c r="D2" t="n">
+        <v>302964.475127336</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.4428839469499368</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-1.065044201242643</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3009347841709681</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Non-operated</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3" t="n">
+        <v>711429.048437673</v>
+      </c>
+      <c r="D3" t="n">
+        <v>321945.0610452036</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.452532914915701</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-1.065044201242643</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3009347841709681</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Arm</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>CofV</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>t-statistic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>p-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Operated</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C2" t="n">
         <v>66661.73394939637</v>
       </c>
       <c r="D2" t="n">
